--- a/images_src/compare.xlsx
+++ b/images_src/compare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LynxPeng\projects\GraduationProjectRecords\paper\images_src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF810637-B627-4050-B2C2-F8EF67C2E458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723B516B-E463-470C-8168-0083C0E31F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{EDDC3588-FA81-412B-9C2E-BC5FA0B2AF09}"/>
   </bookViews>
@@ -146,6 +146,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFED06F"/>
+      <color rgb="FF72BDD7"/>
+      <color rgb="FF386694"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -178,12 +185,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -191,19 +195,33 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="zh-CN" altLang="en-US" sz="1200" b="1">
+              <a:rPr lang="zh-CN" altLang="en-US" sz="1600" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
                 <a:latin typeface="宋体" panose="02010600030101010101" pitchFamily="2" charset="-122"/>
                 <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="2" charset="-122"/>
               </a:rPr>
               <a:t>注册方案对比测试结果</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1200" b="1">
+            <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1600" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
               <a:latin typeface="宋体" panose="02010600030101010101" pitchFamily="2" charset="-122"/>
               <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="2" charset="-122"/>
             </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.24403625036240081"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -217,12 +235,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -235,7 +250,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11554021738504099"/>
+          <c:y val="0.17463022036163098"/>
+          <c:w val="0.83123716908080458"/>
+          <c:h val="0.58237686241494113"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -248,7 +273,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="386694"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -306,7 +331,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="FED06F"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -377,6 +402,42 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  </a:rPr>
+                  <a:t>并发度</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47128336169951951"/>
+              <c:y val="0.82134758127428187"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -392,13 +453,10 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="tx1"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
+                  <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
@@ -407,17 +465,14 @@
           </c:txPr>
         </c:title>
         <c:numFmt formatCode="0_ " sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="in"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -471,14 +526,85 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US" sz="1000" b="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  </a:rPr>
+                  <a:t>时钟周期</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.8890365578788972E-5"/>
+              <c:y val="7.5325486521832491E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0_ " sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="in"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln>
-            <a:noFill/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -519,6 +645,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.28989008588392223"/>
+          <c:y val="0.88807080771300417"/>
+          <c:w val="0.43818057238406399"/>
+          <c:h val="7.8017842821971856E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1135,15 +1271,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>177483</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>155713</xdr:rowOff>
+      <xdr:colOff>177484</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>51589</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>848018</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>25085</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>12562</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/images_src/compare.xlsx
+++ b/images_src/compare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LynxPeng\projects\GraduationProjectRecords\paper\images_src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723B516B-E463-470C-8168-0083C0E31F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7837DCFD-6288-47E4-AA01-163EB30A481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{EDDC3588-FA81-412B-9C2E-BC5FA0B2AF09}"/>
+    <workbookView xWindow="-69" yWindow="-69" windowWidth="22080" windowHeight="13132" xr2:uid="{EDDC3588-FA81-412B-9C2E-BC5FA0B2AF09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -269,7 +269,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>持续性注册</c:v>
+            <c:v>持久绑定</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -327,7 +327,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>一次性注册</c:v>
+            <c:v>单次绑定</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -529,7 +529,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -575,7 +575,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
